--- a/CodeCC/申万一级行业月度收益率矩阵.xlsx
+++ b/CodeCC/申万一级行业月度收益率矩阵.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>2025-01</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
   <si>
     <t>估值类型</t>
@@ -539,10 +542,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,10 +621,13 @@
       <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>-2.136559794551374</v>
@@ -678,12 +684,15 @@
         <v>-13.75741568317155</v>
       </c>
       <c r="T2">
-        <v>10.81163110283019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
+        <v>10.22316272246717</v>
+      </c>
+      <c r="U2">
+        <v>-1.52307134266243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>-4.325203366751573</v>
@@ -740,12 +749,15 @@
         <v>-19.74154515052091</v>
       </c>
       <c r="T3">
-        <v>13.65363573758227</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
+        <v>11.50970240821079</v>
+      </c>
+      <c r="U3">
+        <v>-0.4966998976438819</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>5.391412430434506</v>
@@ -802,12 +814,15 @@
         <v>-3.303392592490151</v>
       </c>
       <c r="T4">
-        <v>-4.850046637351769</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26">
+        <v>-6.580625511583205</v>
+      </c>
+      <c r="U4">
+        <v>6.967034934274463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>1.538988326848245</v>
@@ -864,12 +879,15 @@
         <v>3.447939050595816</v>
       </c>
       <c r="T5">
-        <v>-14.77204682104157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
+        <v>-15.65342750038963</v>
+      </c>
+      <c r="U5">
+        <v>3.772256287900433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>0.7903891781213979</v>
@@ -926,12 +944,15 @@
         <v>-10.03386235433133</v>
       </c>
       <c r="T6">
-        <v>-0.4217760042177443</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
+        <v>1.129432511294337</v>
+      </c>
+      <c r="U6">
+        <v>-0.9177769403001523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>-1.232919142226163</v>
@@ -988,12 +1009,15 @@
         <v>-11.77451224969014</v>
       </c>
       <c r="T7">
-        <v>1.815124324463091</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
+        <v>3.388488808444889</v>
+      </c>
+      <c r="U7">
+        <v>-0.595502841611073</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>-0.8653542874174192</v>
@@ -1050,12 +1074,15 @@
         <v>-5.415059281697754</v>
       </c>
       <c r="T8">
-        <v>-13.57171523196197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
+        <v>-14.43531357715374</v>
+      </c>
+      <c r="U8">
+        <v>3.626156880594755</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>-2.926143623818045</v>
@@ -1112,12 +1139,15 @@
         <v>1.385867331561519</v>
       </c>
       <c r="T9">
-        <v>-15.26353280167958</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
+        <v>-15.45794883055813</v>
+      </c>
+      <c r="U9">
+        <v>3.357667899087935</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>3.50801358899373</v>
@@ -1174,12 +1204,15 @@
         <v>7.836048275946683</v>
       </c>
       <c r="T10">
-        <v>-19.37911535178637</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
+        <v>-21.6890470674308</v>
+      </c>
+      <c r="U10">
+        <v>6.675456991470785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>-2.707095675293925</v>
@@ -1236,12 +1269,15 @@
         <v>-5.021169095459765</v>
       </c>
       <c r="T11">
-        <v>-8.361976317496577</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26">
+        <v>-7.434427737381755</v>
+      </c>
+      <c r="U11">
+        <v>1.041445050411749</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>0.1427601214154084</v>
@@ -1298,12 +1334,15 @@
         <v>18.71378130377468</v>
       </c>
       <c r="T12">
-        <v>-26.94399588252324</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
+        <v>-27.22745842313508</v>
+      </c>
+      <c r="U12">
+        <v>6.338502788737221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>-1.472801744191343</v>
@@ -1360,12 +1399,15 @@
         <v>-10.0456431151888</v>
       </c>
       <c r="T13">
-        <v>3.039397357396068</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+        <v>5.59085965194972</v>
+      </c>
+      <c r="U13">
+        <v>-1.015796557342219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14">
         <v>-1.973498031466747</v>
@@ -1422,12 +1464,15 @@
         <v>-10.66800153367701</v>
       </c>
       <c r="T14">
-        <v>-9.443375783359787</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26">
+        <v>-7.098093727037435</v>
+      </c>
+      <c r="U14">
+        <v>2.25857393998985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15">
         <v>-2.660958184942797</v>
@@ -1484,12 +1529,15 @@
         <v>-15.06309366026066</v>
       </c>
       <c r="T15">
-        <v>2.362718527444274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
+        <v>0.3462811803184307</v>
+      </c>
+      <c r="U15">
+        <v>-1.271420238677035</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16">
         <v>-2.124505928853759</v>
@@ -1546,12 +1594,15 @@
         <v>-6.349940968122791</v>
       </c>
       <c r="T16">
-        <v>-9.667369465459497</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>-9.206002728512953</v>
+      </c>
+      <c r="U16">
+        <v>2.549748920705897</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>3.993748022161436</v>
@@ -1608,12 +1659,15 @@
         <v>-11.45525472630902</v>
       </c>
       <c r="T17">
-        <v>-5.117466233075085</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>-2.461793133392731</v>
+      </c>
+      <c r="U17">
+        <v>1.420790615141954</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>-9.425700085389622</v>
@@ -1670,12 +1724,15 @@
         <v>-14.55286909414387</v>
       </c>
       <c r="T18">
-        <v>-2.880809888062874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>2.414263632606151</v>
+      </c>
+      <c r="U18">
+        <v>0.2156583355797714</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19">
         <v>-0.4532428588726711</v>
@@ -1732,12 +1789,15 @@
         <v>-5.785046676319306</v>
       </c>
       <c r="T19">
-        <v>0.3325421856725574</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>3.694624098428712</v>
+      </c>
+      <c r="U19">
+        <v>0.1593852316848166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20">
         <v>-5.072943600987068</v>
@@ -1794,12 +1854,15 @@
         <v>-11.31979198797692</v>
       </c>
       <c r="T20">
-        <v>5.245182601478504</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>10.05455401862592</v>
+      </c>
+      <c r="U20">
+        <v>-2.763367697594499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>-2.687748092113174</v>
@@ -1856,12 +1919,15 @@
         <v>-8.008483196981553</v>
       </c>
       <c r="T21">
-        <v>-8.00999210806086</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>-3.496585594928292</v>
+      </c>
+      <c r="U21">
+        <v>1.424463228738637</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>-1.591405644895227</v>
@@ -1918,12 +1984,15 @@
         <v>-2.784648656181254</v>
       </c>
       <c r="T22">
-        <v>1.639215925631565</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>0.6158006403477412</v>
+      </c>
+      <c r="U22">
+        <v>3.053733622486043</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>-2.403045204769194</v>
@@ -1980,12 +2049,15 @@
         <v>-9.434751568742882</v>
       </c>
       <c r="T23">
-        <v>-10.54204731787304</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>-5.073921627681299</v>
+      </c>
+      <c r="U23">
+        <v>2.315515696578685</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>-2.880910784325064</v>
@@ -2042,12 +2114,15 @@
         <v>-13.24662508048088</v>
       </c>
       <c r="T24">
-        <v>1.86470000713419</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>6.279279921999481</v>
+      </c>
+      <c r="U24">
+        <v>-0.7208011021046068</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25">
         <v>3.436204988288605</v>
@@ -2104,12 +2179,15 @@
         <v>33.29381338066995</v>
       </c>
       <c r="T25">
-        <v>-26.42830580497976</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>-33.39010316342775</v>
+      </c>
+      <c r="U25">
+        <v>11.71431264877094</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26">
         <v>1.983879207583583</v>
@@ -2166,12 +2244,15 @@
         <v>-6.159470952565038</v>
       </c>
       <c r="T26">
-        <v>-6.018540527691929</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>-4.402619011604036</v>
+      </c>
+      <c r="U26">
+        <v>5.505544683626873</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27">
         <v>2.190895151995531</v>
@@ -2228,12 +2309,15 @@
         <v>15.10398148761924</v>
       </c>
       <c r="T27">
-        <v>-18.70329658399422</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>-29.3906775014792</v>
+      </c>
+      <c r="U27">
+        <v>7.598985517000867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28">
         <v>1.569311246730587</v>
@@ -2290,12 +2374,15 @@
         <v>-12.77406679764244</v>
       </c>
       <c r="T28">
-        <v>-6.194900765628475</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>2.064966921876166</v>
+      </c>
+      <c r="U28">
+        <v>3.678968443268715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29">
         <v>2.605197841773643</v>
@@ -2352,12 +2439,15 @@
         <v>-7.27344399493608</v>
       </c>
       <c r="T29">
-        <v>7.540962299250209</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>10.86100031681303</v>
+      </c>
+      <c r="U29">
+        <v>-3.851436934604358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B30">
         <v>-1.414887023158851</v>
@@ -2414,12 +2504,15 @@
         <v>1.550649896156631</v>
       </c>
       <c r="T30">
-        <v>-0.5435886735887352</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>-1.668103424608647</v>
+      </c>
+      <c r="U30">
+        <v>-0.4420339134215578</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B31">
         <v>-4.513564740162379</v>
@@ -2476,12 +2569,15 @@
         <v>-11.61404623665231</v>
       </c>
       <c r="T31">
-        <v>-4.80775873521988</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>-2.783047694964791</v>
+      </c>
+      <c r="U31">
+        <v>1.135180848295603</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B32">
         <v>-2.964729252555209</v>
@@ -2538,7 +2634,10 @@
         <v>-7.511355599552017</v>
       </c>
       <c r="T32">
-        <v>-14.68461176962038</v>
+        <v>-16.02309714027117</v>
+      </c>
+      <c r="U32">
+        <v>5.551823586158822</v>
       </c>
     </row>
   </sheetData>
